--- a/menu and price.xlsx
+++ b/menu and price.xlsx
@@ -1,21 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11028"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/leo/Desktop/ latte lab menu/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Shun\github\LATTE-LAB---Telegram\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABD1C4E2-A6E0-C24D-BDE0-832B23769711}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{286A7DCB-BC7C-4587-88CC-897154BDE4D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="620" windowWidth="28800" windowHeight="15560" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表 1 - production_detail" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -44,9 +57,6 @@
   </si>
   <si>
     <t>Hot Cappuccino</t>
-  </si>
-  <si>
-    <t>Hot Caffe Condensed Milk</t>
   </si>
   <si>
     <t>Hot Matcha Latte</t>
@@ -428,6 +438,10 @@
     <t>Hot Espresso</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
+  <si>
+    <t>Hot Caffe with Condensed Milk</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -437,7 +451,7 @@
     <numFmt numFmtId="176" formatCode="\$#,##0.00"/>
     <numFmt numFmtId="177" formatCode="[$KHR]\ #,##0_);[Red]\([$KHR]\ #,##0\)"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <sz val="10"/>
       <color indexed="8"/>
@@ -518,6 +532,12 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="DaunPenh"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color indexed="8"/>
+      <name val="Helvetica Neue"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="5">
@@ -678,7 +698,7 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -760,13 +780,16 @@
     <xf numFmtId="49" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -1900,28 +1923,28 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I50"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.33203125" defaultRowHeight="20" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="8.28515625" defaultRowHeight="20.100000000000001" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="3.83203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="17.83203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="24.1640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="11.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.6640625" style="25" customWidth="1"/>
-    <col min="7" max="7" width="13.83203125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="24.5" style="1" customWidth="1"/>
-    <col min="9" max="9" width="15.33203125" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="8.33203125" style="1"/>
+    <col min="1" max="1" width="3.85546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.7109375" style="25" customWidth="1"/>
+    <col min="7" max="7" width="13.85546875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="24.42578125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="15.28515625" style="1" customWidth="1"/>
+    <col min="10" max="16384" width="8.28515625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="27.75" customHeight="1">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
       <c r="F1" s="21"/>
       <c r="G1" s="10"/>
     </row>
@@ -1936,22 +1959,22 @@
         <v>3</v>
       </c>
       <c r="D2" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="G2" s="17" t="s">
+        <v>106</v>
+      </c>
+      <c r="H2" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="F2" s="26" t="s">
-        <v>105</v>
-      </c>
-      <c r="G2" s="17" t="s">
+      <c r="I2" s="2" t="s">
         <v>107</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="20.25" customHeight="1">
@@ -1965,7 +1988,7 @@
         <v>5</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E3" s="15">
         <v>1.5</v>
@@ -1977,11 +2000,11 @@
         <v>4000</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I3" s="9"/>
     </row>
-    <row r="4" spans="1:9" ht="20" customHeight="1">
+    <row r="4" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A4" s="6">
         <v>2</v>
       </c>
@@ -1992,7 +2015,7 @@
         <v>6</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E4" s="16">
         <v>1.8</v>
@@ -2004,11 +2027,11 @@
         <v>5000</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I4" s="9"/>
     </row>
-    <row r="5" spans="1:9" ht="20" customHeight="1">
+    <row r="5" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A5" s="6">
         <v>3</v>
       </c>
@@ -2019,7 +2042,7 @@
         <v>7</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E5" s="16">
         <v>1.8</v>
@@ -2031,22 +2054,22 @@
         <v>5000</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I5" s="9"/>
     </row>
-    <row r="6" spans="1:9" ht="20" customHeight="1">
+    <row r="6" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A6" s="3">
         <v>4</v>
       </c>
       <c r="B6" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="8" t="s">
-        <v>8</v>
+      <c r="C6" s="30" t="s">
+        <v>110</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E6" s="16">
         <v>1.8</v>
@@ -2058,11 +2081,11 @@
         <v>5000</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I6" s="9"/>
     </row>
-    <row r="7" spans="1:9" ht="20" customHeight="1">
+    <row r="7" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A7" s="6">
         <v>5</v>
       </c>
@@ -2070,10 +2093,10 @@
         <v>4</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E7" s="16">
         <v>1.8</v>
@@ -2085,11 +2108,11 @@
         <v>5000</v>
       </c>
       <c r="H7" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I7" s="9"/>
     </row>
-    <row r="8" spans="1:9" ht="20" customHeight="1">
+    <row r="8" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A8" s="6">
         <v>6</v>
       </c>
@@ -2097,10 +2120,10 @@
         <v>4</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E8" s="16">
         <v>1.8</v>
@@ -2112,11 +2135,11 @@
         <v>5000</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I8" s="9"/>
     </row>
-    <row r="9" spans="1:9" ht="20" customHeight="1">
+    <row r="9" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A9" s="3">
         <v>7</v>
       </c>
@@ -2124,10 +2147,10 @@
         <v>4</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E9" s="16">
         <v>1.8</v>
@@ -2139,11 +2162,11 @@
         <v>5000</v>
       </c>
       <c r="H9" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I9" s="9"/>
     </row>
-    <row r="10" spans="1:9" ht="20" customHeight="1">
+    <row r="10" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A10" s="6">
         <v>8</v>
       </c>
@@ -2151,10 +2174,10 @@
         <v>4</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E10" s="16">
         <v>1.3</v>
@@ -2166,22 +2189,22 @@
         <v>4000</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I10" s="9"/>
     </row>
-    <row r="11" spans="1:9" ht="20" customHeight="1">
+    <row r="11" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A11" s="6">
         <v>9</v>
       </c>
       <c r="B11" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C11" s="28" t="s">
-        <v>110</v>
-      </c>
-      <c r="D11" s="29" t="s">
+      <c r="C11" s="27" t="s">
         <v>109</v>
+      </c>
+      <c r="D11" s="28" t="s">
+        <v>108</v>
       </c>
       <c r="E11" s="16">
         <v>1.3</v>
@@ -2193,22 +2216,22 @@
         <v>4000</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I11" s="9"/>
     </row>
-    <row r="12" spans="1:9" ht="20" customHeight="1">
+    <row r="12" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A12" s="3">
         <v>10</v>
       </c>
       <c r="B12" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="8" t="s">
-        <v>14</v>
-      </c>
       <c r="D12" s="8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E12" s="16">
         <v>2</v>
@@ -2220,22 +2243,22 @@
         <v>6000</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I12" s="9"/>
     </row>
-    <row r="13" spans="1:9" ht="20" customHeight="1">
+    <row r="13" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A13" s="6">
         <v>11</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E13" s="16">
         <v>2</v>
@@ -2247,22 +2270,22 @@
         <v>6000</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I13" s="9"/>
     </row>
-    <row r="14" spans="1:9" ht="20" customHeight="1">
+    <row r="14" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A14" s="6">
         <v>12</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E14" s="16">
         <v>2</v>
@@ -2274,22 +2297,22 @@
         <v>6000</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I14" s="9"/>
     </row>
-    <row r="15" spans="1:9" ht="20" customHeight="1">
+    <row r="15" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A15" s="3">
         <v>13</v>
       </c>
       <c r="B15" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="C15" s="8" t="s">
-        <v>18</v>
-      </c>
       <c r="D15" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E15" s="16">
         <v>1.8</v>
@@ -2301,22 +2324,22 @@
         <v>5000</v>
       </c>
       <c r="H15" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I15" s="9"/>
     </row>
-    <row r="16" spans="1:9" ht="20" customHeight="1">
+    <row r="16" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A16" s="6">
         <v>14</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E16" s="16">
         <v>1.8</v>
@@ -2328,22 +2351,22 @@
         <v>5000</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I16" s="9"/>
     </row>
-    <row r="17" spans="1:9" ht="20" customHeight="1">
+    <row r="17" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A17" s="6">
         <v>15</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E17" s="16">
         <v>1.8</v>
@@ -2355,22 +2378,22 @@
         <v>5000</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I17" s="9"/>
     </row>
-    <row r="18" spans="1:9" ht="20" customHeight="1">
+    <row r="18" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A18" s="3">
         <v>16</v>
       </c>
       <c r="B18" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C18" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="C18" s="8" t="s">
-        <v>22</v>
-      </c>
       <c r="D18" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E18" s="16">
         <v>1.5</v>
@@ -2382,22 +2405,22 @@
         <v>4000</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I18" s="9"/>
     </row>
-    <row r="19" spans="1:9" ht="20" customHeight="1">
+    <row r="19" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A19" s="6">
         <v>17</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E19" s="16">
         <v>1.8</v>
@@ -2409,22 +2432,22 @@
         <v>5000</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I19" s="9"/>
     </row>
-    <row r="20" spans="1:9" ht="20" customHeight="1">
+    <row r="20" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A20" s="6">
         <v>18</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E20" s="16">
         <v>1.8</v>
@@ -2436,22 +2459,22 @@
         <v>5000</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I20" s="9"/>
     </row>
-    <row r="21" spans="1:9" ht="20" customHeight="1">
+    <row r="21" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A21" s="3">
         <v>19</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E21" s="16">
         <v>1.8</v>
@@ -2463,22 +2486,22 @@
         <v>5000</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I21" s="9"/>
     </row>
-    <row r="22" spans="1:9" ht="20" customHeight="1">
+    <row r="22" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A22" s="6">
         <v>20</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E22" s="16">
         <v>1.8</v>
@@ -2490,22 +2513,22 @@
         <v>5000</v>
       </c>
       <c r="H22" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I22" s="9"/>
     </row>
-    <row r="23" spans="1:9" ht="20" customHeight="1">
+    <row r="23" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A23" s="6">
         <v>21</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E23" s="16">
         <v>2</v>
@@ -2517,24 +2540,24 @@
         <v>6000</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I23" s="9">
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="20" customHeight="1">
+    <row r="24" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A24" s="3">
         <v>22</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D24" s="13" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E24" s="16">
         <v>2</v>
@@ -2546,22 +2569,22 @@
         <v>6000</v>
       </c>
       <c r="H24" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I24" s="9"/>
     </row>
-    <row r="25" spans="1:9" ht="20" customHeight="1">
+    <row r="25" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A25" s="6">
         <v>23</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E25" s="16">
         <v>1.3</v>
@@ -2573,22 +2596,22 @@
         <v>4000</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I25" s="9"/>
     </row>
-    <row r="26" spans="1:9" ht="20" customHeight="1">
+    <row r="26" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A26" s="6">
         <v>24</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E26" s="16">
         <v>1.8</v>
@@ -2600,24 +2623,24 @@
         <v>5000</v>
       </c>
       <c r="H26" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I26" s="9">
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="20" customHeight="1">
+    <row r="27" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A27" s="3">
         <v>25</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E27" s="16">
         <v>1.8</v>
@@ -2629,22 +2652,22 @@
         <v>5000</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I27" s="9"/>
     </row>
-    <row r="28" spans="1:9" ht="20" customHeight="1">
+    <row r="28" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A28" s="6">
         <v>26</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E28" s="16">
         <v>1.3</v>
@@ -2656,22 +2679,22 @@
         <v>4000</v>
       </c>
       <c r="H28" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I28" s="9"/>
     </row>
-    <row r="29" spans="1:9" ht="20" customHeight="1">
+    <row r="29" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A29" s="6">
         <v>27</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E29" s="16">
         <v>2.2000000000000002</v>
@@ -2683,24 +2706,24 @@
         <v>6000</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I29" s="9">
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="20" customHeight="1">
+    <row r="30" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A30" s="3">
         <v>28</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D30" s="13" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E30" s="16">
         <v>1.8</v>
@@ -2712,22 +2735,22 @@
         <v>5000</v>
       </c>
       <c r="H30" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I30" s="9"/>
     </row>
-    <row r="31" spans="1:9" ht="20" customHeight="1">
+    <row r="31" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A31" s="6">
         <v>29</v>
       </c>
       <c r="B31" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C31" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="C31" s="8" t="s">
-        <v>34</v>
-      </c>
       <c r="D31" s="14" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E31" s="16">
         <v>2.5</v>
@@ -2739,22 +2762,22 @@
         <v>7000</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I31" s="9"/>
     </row>
-    <row r="32" spans="1:9" ht="20" customHeight="1">
+    <row r="32" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A32" s="6">
         <v>30</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E32" s="16">
         <v>2.5</v>
@@ -2766,22 +2789,22 @@
         <v>7000</v>
       </c>
       <c r="H32" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I32" s="9"/>
     </row>
-    <row r="33" spans="1:9" ht="20" customHeight="1">
+    <row r="33" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A33" s="3">
         <v>31</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E33" s="16">
         <v>2.5</v>
@@ -2793,24 +2816,24 @@
         <v>7000</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I33" s="9">
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="20" customHeight="1">
+    <row r="34" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A34" s="6">
         <v>32</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E34" s="16">
         <v>2.5</v>
@@ -2822,22 +2845,22 @@
         <v>7000</v>
       </c>
       <c r="H34" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I34" s="9"/>
     </row>
-    <row r="35" spans="1:9" ht="20" customHeight="1">
+    <row r="35" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A35" s="6">
         <v>33</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E35" s="16">
         <v>2.5</v>
@@ -2849,22 +2872,22 @@
         <v>7000</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I35" s="9"/>
     </row>
-    <row r="36" spans="1:9" ht="20" customHeight="1">
+    <row r="36" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A36" s="3">
         <v>34</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D36" s="8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E36" s="16">
         <v>2.5</v>
@@ -2876,22 +2899,22 @@
         <v>7000</v>
       </c>
       <c r="H36" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I36" s="9"/>
     </row>
-    <row r="37" spans="1:9" ht="20" customHeight="1">
+    <row r="37" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A37" s="6">
         <v>35</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E37" s="16">
         <v>2.5</v>
@@ -2903,22 +2926,22 @@
         <v>7000</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I37" s="9"/>
     </row>
-    <row r="38" spans="1:9" ht="20" customHeight="1">
+    <row r="38" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A38" s="6">
         <v>36</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D38" s="14" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E38" s="16">
         <v>2.5</v>
@@ -2930,22 +2953,22 @@
         <v>7000</v>
       </c>
       <c r="H38" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I38" s="9"/>
     </row>
-    <row r="39" spans="1:9" ht="20" customHeight="1">
+    <row r="39" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A39" s="3">
         <v>37</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E39" s="16">
         <v>1.3</v>
@@ -2957,22 +2980,22 @@
         <v>4000</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I39" s="9"/>
     </row>
-    <row r="40" spans="1:9" ht="20" customHeight="1">
+    <row r="40" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A40" s="6">
         <v>38</v>
       </c>
       <c r="B40" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C40" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="C40" s="8" t="s">
-        <v>41</v>
-      </c>
       <c r="D40" s="8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E40" s="16">
         <v>1.3</v>
@@ -2984,22 +3007,22 @@
         <v>4000</v>
       </c>
       <c r="H40" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I40" s="9"/>
     </row>
-    <row r="41" spans="1:9" ht="20" customHeight="1">
+    <row r="41" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A41" s="6">
         <v>39</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D41" s="8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E41" s="16">
         <v>1.3</v>
@@ -3011,22 +3034,22 @@
         <v>4000</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I41" s="9"/>
     </row>
-    <row r="42" spans="1:9" ht="20" customHeight="1">
+    <row r="42" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A42" s="3">
         <v>40</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D42" s="8" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E42" s="16">
         <v>1.3</v>
@@ -3038,22 +3061,22 @@
         <v>4000</v>
       </c>
       <c r="H42" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I42" s="9"/>
     </row>
-    <row r="43" spans="1:9" ht="20" customHeight="1">
+    <row r="43" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A43" s="6">
         <v>41</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D43" s="8" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E43" s="16">
         <v>1.3</v>
@@ -3065,22 +3088,22 @@
         <v>4000</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I43" s="9"/>
     </row>
-    <row r="44" spans="1:9" ht="20" customHeight="1">
+    <row r="44" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A44" s="6">
         <v>42</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D44" s="8" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E44" s="16">
         <v>1.3</v>
@@ -3092,22 +3115,22 @@
         <v>4000</v>
       </c>
       <c r="H44" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I44" s="9"/>
     </row>
-    <row r="45" spans="1:9" ht="20" customHeight="1">
+    <row r="45" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A45" s="3">
         <v>43</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D45" s="8" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E45" s="16">
         <v>1.3</v>
@@ -3119,22 +3142,22 @@
         <v>4000</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I45" s="9"/>
     </row>
-    <row r="46" spans="1:9" ht="20" customHeight="1">
+    <row r="46" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A46" s="6">
         <v>44</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D46" s="8" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E46" s="16">
         <v>1.8</v>
@@ -3146,22 +3169,22 @@
         <v>5000</v>
       </c>
       <c r="H46" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I46" s="9"/>
     </row>
-    <row r="47" spans="1:9" ht="20" customHeight="1">
+    <row r="47" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A47" s="6">
         <v>45</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C47" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D47" s="8" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E47" s="16">
         <v>1.8</v>
@@ -3173,22 +3196,22 @@
         <v>5000</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I47" s="9"/>
     </row>
-    <row r="48" spans="1:9" ht="20" customHeight="1">
+    <row r="48" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A48" s="3">
         <v>46</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C48" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D48" s="8" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E48" s="16">
         <v>1.8</v>
@@ -3200,22 +3223,22 @@
         <v>5000</v>
       </c>
       <c r="H48" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I48" s="9"/>
     </row>
-    <row r="49" spans="1:9" ht="20" customHeight="1">
+    <row r="49" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A49" s="6">
         <v>47</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C49" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D49" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E49" s="16">
         <v>1.8</v>
@@ -3227,22 +3250,22 @@
         <v>5000</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I49" s="9"/>
     </row>
-    <row r="50" spans="1:9" ht="20" customHeight="1">
+    <row r="50" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A50" s="6">
         <v>48</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C50" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D50" s="8" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E50" s="16">
         <v>1.8</v>
@@ -3254,7 +3277,7 @@
         <v>5000</v>
       </c>
       <c r="H50" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I50" s="9"/>
     </row>
@@ -3264,7 +3287,7 @@
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
-  <pageSetup scale="51" orientation="portrait" r:id="rId1"/>
+  <pageSetup scale="61" orientation="portrait" r:id="rId1"/>
   <headerFooter>
     <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;11&amp;K000000&amp;P</oddFooter>
   </headerFooter>
